--- a/reports/meta_intel_2026-W25.xlsx
+++ b/reports/meta_intel_2026-W25.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-15 10:57 UTC</t>
+          <t>Generated: 2026-06-15 18:07 UTC</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
@@ -537,7 +537,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>Remento</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -547,11 +547,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -665,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1865,36 +1865,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Remento</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1868277354563662</t>
+          <t>1475197920579481</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>enna.care</t>
+          <t>Cortney Belnap, Independent Norwex Consultant with Remento</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>📖 Remento turns recordings into a book of written stories</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>213</v>
+        <v>4</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1362684515702149</t>
+          <t>1868277354563662</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1930,11 +1930,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>48</v>
+        <v>213</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1938930663325095</t>
+          <t>1362684515702149</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1970,11 +1970,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1852060685669387</t>
+          <t>1938930663325095</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2010,11 +2010,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>966816482430409</t>
+          <t>1852060685669387</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>54</v>
+        <v>220</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1588345672369492</t>
+          <t>966816482430409</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2090,11 +2090,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>841302105060560</t>
+          <t>1588345672369492</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2130,11 +2130,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1296748252140081</t>
+          <t>841302105060560</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3976129939359406</t>
+          <t>1296748252140081</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1943193019573119</t>
+          <t>3976129939359406</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4072587919646468</t>
+          <t>1943193019573119</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2290,11 +2290,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>64</v>
+        <v>220</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2260190851070799</t>
+          <t>4072587919646468</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2330,11 +2330,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>213</v>
+        <v>64</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>796404973298946</t>
+          <t>2260190851070799</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2370,11 +2370,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3727759467519562</t>
+          <t>796404973298946</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2410,11 +2410,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1893837991150333</t>
+          <t>3727759467519562</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2440,21 +2440,21 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Jetzt enna 30 Tage kostenlos testen! 🎁 Videocalls, Lieblingssendungen oder digitaler Terminkalender: enna holt die schönen Seiten moderner Technik ins Wohnzimmer deiner Großeltern – ganz ohne Technikstress. ✨ Was enna möglich macht:</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>✅ Digitale Fotoalben für gemeinsame Momente</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>56</v>
+        <v>213</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1549478262721918</t>
+          <t>1893837991150333</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2480,21 +2480,21 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Jetzt enna 30 Tage kostenlos testen! 🎁 Videocalls, Lieblingssendungen oder digitaler Terminkalender: enna holt die schönen Seiten moderner Technik ins Wohnzimmer deiner Großeltern – ganz ohne Technikstress. ✨ Was enna möglich macht:</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kein Kauf, keine Einrichtung.</t>
+          <t>✅ Digitale Fotoalben für gemeinsame Momente</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1171548231746967</t>
+          <t>1549478262721918</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2530,11 +2530,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>848561304926655</t>
+          <t>1171548231746967</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2570,11 +2570,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>54</v>
+        <v>212</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>871339118687590</t>
+          <t>848561304926655</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2610,11 +2610,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2761672647588250</t>
+          <t>871339118687590</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2650,11 +2650,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1628987998235230</t>
+          <t>2761672647588250</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2690,11 +2690,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>804595359053733</t>
+          <t>1628987998235230</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2730,11 +2730,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1373162224393589</t>
+          <t>804595359053733</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2770,11 +2770,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>25607802815471461</t>
+          <t>1373162224393589</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2810,11 +2810,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1896813954581984</t>
+          <t>25607802815471461</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2850,11 +2850,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1136736145294473</t>
+          <t>1896813954581984</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2890,11 +2890,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>33</v>
+        <v>220</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>809944418627988</t>
+          <t>1136736145294473</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2930,11 +2930,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>220</v>
+        <v>33</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>779152008120335</t>
+          <t>809944418627988</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2970,11 +2970,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4246986475583692</t>
+          <t>779152008120335</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3010,11 +3010,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1705688694195534</t>
+          <t>4246986475583692</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3050,11 +3050,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3065,41 +3065,36 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1631994437866750</t>
+          <t>1705688694195534</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>StoryKeeper</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3115,7 +3110,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1029328920037241</t>
+          <t>1631994437866750</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3125,7 +3120,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3160,7 +3155,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1023631550111017</t>
+          <t>1029328920037241</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3170,17 +3165,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Storykeeper helps capture your loved one’s voice, guiding each question and turning it into a book you’ll treasure forever. WWW.STORYKEEPER.COM Because memories fade, but stories shouldn’t.</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Because memories fade, but stories shouldn’t.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3205,7 +3200,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1888598388471432</t>
+          <t>1023631550111017</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3215,21 +3210,26 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>Storykeeper helps capture your loved one’s voice, guiding each question and turning it into a book you’ll treasure forever. WWW.STORYKEEPER.COM Because memories fade, but stories shouldn’t.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Because memories fade, but stories shouldn’t.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4564425283883218</t>
+          <t>1888598388471432</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3263,18 +3263,13 @@
           <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Learn more</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3290,7 +3285,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1333466355410690</t>
+          <t>4564425283883218</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3300,17 +3295,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
+          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>This Book Made My Dad Cry (In a Good Way).</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3335,7 +3330,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2071219660470847</t>
+          <t>1333466355410690</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3360,11 +3355,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3380,7 +3375,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1496684578006716</t>
+          <t>2071219660470847</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3390,26 +3385,26 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Learn more</t>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3425,7 +3420,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>969167216028774</t>
+          <t>1496684578006716</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3435,7 +3430,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3470,7 +3465,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2165050094062397</t>
+          <t>969167216028774</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3480,7 +3475,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3515,7 +3510,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1217928917027025</t>
+          <t>2165050094062397</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3525,7 +3520,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Skip the typing, editing, and overwhelm. Storykeeper records voices naturally and turns them into a handcrafted book. Effortless, modern and filled with the moments that matter most. Sorry, we're having trouble playing this video.</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3540,11 +3535,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3560,7 +3555,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1012871601217194</t>
+          <t>1217928917027025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3570,21 +3565,26 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>Skip the typing, editing, and overwhelm. Storykeeper records voices naturally and turns them into a handcrafted book. Effortless, modern and filled with the moments that matter most. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>26907492185598691</t>
+          <t>1012871601217194</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3610,21 +3610,21 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Give more than a gift—give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.UK The Gift They’ll Never Forget.</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Give a gift that becomes a family heirloom—one story at a time.</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2438857833193853</t>
+          <t>26907492185598691</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3650,21 +3650,21 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>Give more than a gift—give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.UK The Gift They’ll Never Forget.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>Give a gift that becomes a family heirloom—one story at a time.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1305482504525889</t>
+          <t>2438857833193853</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3690,26 +3690,21 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>This Book Made My Dad Cry (In a Good Way).</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Shop Now</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3725,7 +3720,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2308717926326835</t>
+          <t>1305482504525889</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3735,21 +3730,26 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>Give more than a gift. Give your family a keepsake that grows more meaningful with time. WWW.STORYKEEPER.COM This Book Made My Dad Cry (In a Good Way).</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>This Book Made My Dad Cry (In a Good Way).</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1726022011744222</t>
+          <t>2308717926326835</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3775,26 +3775,21 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3810,7 +3805,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1930719370943178</t>
+          <t>1726022011744222</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3820,7 +3815,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3828,13 +3823,18 @@
           <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Learn more</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>941061762318804</t>
+          <t>1930719370943178</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>974049545525369</t>
+          <t>941061762318804</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3908,18 +3908,13 @@
           <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Learn more</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3935,7 +3930,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>973998952205878</t>
+          <t>974049545525369</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3945,26 +3940,26 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>The Only Book That Let's You Listen to Their Story.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3980,7 +3975,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>998741643007745</t>
+          <t>973998952205878</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3990,21 +3985,26 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
+          <t>The Only Book That Let's You Listen to Their Story.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1547908606933797</t>
+          <t>998741643007745</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2265135094294745</t>
+          <t>1547908606933797</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4070,26 +4070,21 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>StoryKeeper makes it easy to capture memories. No setup, no stress, no tech overwhelm. Just stories, told and transformed beautifully. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4105,7 +4100,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>884035753955138</t>
+          <t>2265135094294745</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4115,17 +4110,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Interview by voice, add photos, and we turn it into a keepsake: two hardcovers + e-book. WWW.STORYKEEPER.COM Record. Print. Keep Forever</t>
+          <t>StoryKeeper makes it easy to capture memories. No setup, no stress, no tech overwhelm. Just stories, told and transformed beautifully. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Record. Print. Keep Forever</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4150,7 +4145,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1307636784329203</t>
+          <t>884035753955138</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4160,17 +4155,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>It looks like a book, but it speaks from the heart. StoryKeeper turns voices and memories into something you can open, hold, and hear. Sorry, we're having trouble playing this video.</t>
+          <t>Interview by voice, add photos, and we turn it into a keepsake: two hardcovers + e-book. WWW.STORYKEEPER.COM Record. Print. Keep Forever</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
+          <t>Record. Print. Keep Forever</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Learn more</t>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4195,7 +4190,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>824548033811820</t>
+          <t>1307636784329203</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4205,7 +4200,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
+          <t>It looks like a book, but it speaks from the heart. StoryKeeper turns voices and memories into something you can open, hold, and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4240,7 +4235,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1314583030805433</t>
+          <t>824548033811820</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4250,26 +4245,26 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Interview by voice, add photos, and we turn it into a keepsake: two hardcovers + e-book. WWW.STORYKEEPER.COM Record. Print. Keep Forever</t>
+          <t>This Father’s Day, capture the stories that matter before they fade. StoryKeeper turns memories into a book your family can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Record. Print. Keep Forever</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4285,7 +4280,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>26967277692911798</t>
+          <t>1314583030805433</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4295,21 +4290,26 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
+          <t>Interview by voice, add photos, and we turn it into a keepsake: two hardcovers + e-book. WWW.STORYKEEPER.COM Record. Print. Keep Forever</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Low impression count</t>
+          <t>Record. Print. Keep Forever</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4320,41 +4320,36 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ElliQ</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1685628942752739</t>
+          <t>26967277692911798</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ElliQ</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+          <t>This Mother's Day, give her a gift that will last forever! Turn her life story into a personalized book filled with memories and love. What would she say if you asked about her most cherished moments?</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>Low impression count</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4370,7 +4365,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1688004719222897</t>
+          <t>1685628942752739</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4395,11 +4390,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4415,7 +4410,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2082672142583809</t>
+          <t>1688004719222897</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4425,7 +4420,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4440,11 +4435,11 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4460,7 +4455,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>25522883924055159</t>
+          <t>2082672142583809</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4470,21 +4465,26 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
+          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>✨ Daily check-ins &amp; reminders</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>838679825886616</t>
+          <t>25522883924055159</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4510,21 +4510,21 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>✨ A friendly voice</t>
+          <t>✨ Daily check-ins &amp; reminders</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1488992326012147</t>
+          <t>838679825886616</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4550,26 +4550,21 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4585,7 +4580,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>944975184903429</t>
+          <t>1488992326012147</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4610,11 +4605,11 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4630,7 +4625,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1682907829804633</t>
+          <t>944975184903429</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4640,7 +4635,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4655,11 +4650,11 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4675,7 +4670,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>993138953210800</t>
+          <t>1682907829804633</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4685,7 +4680,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4700,11 +4695,11 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4720,7 +4715,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1948413482455351</t>
+          <t>993138953210800</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4730,21 +4725,26 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>It’s helping them continue to thrive there ✨</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1456990959516034</t>
+          <t>1948413482455351</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4770,26 +4770,21 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
+          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sorry, we're having trouble playing this video.</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Learn more</t>
+          <t>It’s helping them continue to thrive there ✨</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4805,7 +4800,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>26794090103575688</t>
+          <t>1456990959516034</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4815,21 +4810,26 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
+          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>It’s helping them continue to thrive there ✨</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2383639082136267</t>
+          <t>26794090103575688</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4855,21 +4855,21 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+          <t>What if the way we think about aging actually impacts how we age? The research suggests it does. Positive aging isn’t just a mindset. It can shape real outcomes. That's why ElliQ focuses on helping people feel capable, connected, active, and engaged every day. The goal isn’t just helping people age at home.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>✨ A friendly voice</t>
+          <t>It’s helping them continue to thrive there ✨</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1764899438019092</t>
+          <t>2383639082136267</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4905,11 +4905,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4925,33 +4925,73 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
+          <t>1764899438019092</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>✨ A friendly voice</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>34</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>3778152075652558</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>ElliQ</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>✨ A friendly voice</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="I103" t="n">
+      <c r="I104" t="n">
         <v>24</v>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4968,7 +5008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -4985,7 +5025,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-15 10:57 UTC</t>
+          <t>Generated: 2026-06-15 18:07 UTC</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5044,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -5084,264 +5124,271 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1483707206839148</t>
+          <t>1475197920579481</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1524669709076904</t>
+          <t>1483707206839148</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1536889358035514</t>
+          <t>1524669709076904</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1538314847919342</t>
+          <t>1536889358035514</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1538382194611380</t>
+          <t>1538314847919342</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1547908606933797</t>
+          <t>1538382194611380</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1605458371008781</t>
+          <t>1547908606933797</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1644683516797904</t>
+          <t>1605458371008781</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1672272600747530</t>
+          <t>1644683516797904</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1683371159589008</t>
+          <t>1672272600747530</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1694524915076527</t>
+          <t>1683371159589008</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1705688694195534</t>
+          <t>1694524915076527</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1751531616005068</t>
+          <t>1705688694195534</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1764899438019092</t>
+          <t>1751531616005068</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1896813954581984</t>
+          <t>1764899438019092</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1930719370943178</t>
+          <t>1896813954581984</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2189097101929374</t>
+          <t>1930719370943178</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2230928671076574</t>
+          <t>2189097101929374</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2245313849547808</t>
+          <t>2230928671076574</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2308717926326835</t>
+          <t>2245313849547808</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2397734127385885</t>
+          <t>2308717926326835</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>25607802815471461</t>
+          <t>2397734127385885</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>26967277692911798</t>
+          <t>25607802815471461</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27235511292782176</t>
+          <t>26967277692911798</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27880751554865955</t>
+          <t>27235511292782176</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2910058286010273</t>
+          <t>27880751554865955</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3230644000603975</t>
+          <t>2910058286010273</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4246986475583692</t>
+          <t>3230644000603975</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>779152008120335</t>
+          <t>4246986475583692</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>804595359053733</t>
+          <t>779152008120335</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>809944418627988</t>
+          <t>804595359053733</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>844586681681113</t>
+          <t>809944418627988</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>865940222703351</t>
+          <t>844586681681113</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>908821282230944</t>
+          <t>865940222703351</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>941061762318804</t>
+          <t>908821282230944</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>985688674053578</t>
+          <t>941061762318804</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>992691106795247</t>
+          <t>985688674053578</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
+        <is>
+          <t>992691106795247</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>998741643007745</t>
         </is>
